--- a/artfynd/A 21883-2026 artfynd.xlsx
+++ b/artfynd/A 21883-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136482433</v>
       </c>
       <c r="B2" t="n">
-        <v>104865</v>
+        <v>104868</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21883-2026 artfynd.xlsx
+++ b/artfynd/A 21883-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136482433</v>
       </c>
       <c r="B2" t="n">
-        <v>104868</v>
+        <v>104869</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21883-2026 artfynd.xlsx
+++ b/artfynd/A 21883-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136482433</v>
       </c>
       <c r="B2" t="n">
-        <v>104869</v>
+        <v>104874</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21883-2026 artfynd.xlsx
+++ b/artfynd/A 21883-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136482433</v>
       </c>
       <c r="B2" t="n">
-        <v>104874</v>
+        <v>104876</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21883-2026 artfynd.xlsx
+++ b/artfynd/A 21883-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136482433</v>
       </c>
       <c r="B2" t="n">
-        <v>104876</v>
+        <v>104882</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21883-2026 artfynd.xlsx
+++ b/artfynd/A 21883-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136482433</v>
       </c>
       <c r="B2" t="n">
-        <v>104882</v>
+        <v>104884</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21883-2026 artfynd.xlsx
+++ b/artfynd/A 21883-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136482433</v>
       </c>
       <c r="B2" t="n">
-        <v>104884</v>
+        <v>104885</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21883-2026 artfynd.xlsx
+++ b/artfynd/A 21883-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136482433</v>
       </c>
       <c r="B2" t="n">
-        <v>104885</v>
+        <v>104891</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21883-2026 artfynd.xlsx
+++ b/artfynd/A 21883-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136482433</v>
       </c>
       <c r="B2" t="n">
-        <v>104891</v>
+        <v>104895</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21883-2026 artfynd.xlsx
+++ b/artfynd/A 21883-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136482433</v>
       </c>
       <c r="B2" t="n">
-        <v>104895</v>
+        <v>104968</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21883-2026 artfynd.xlsx
+++ b/artfynd/A 21883-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136482433</v>
       </c>
       <c r="B2" t="n">
-        <v>104968</v>
+        <v>104974</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
